--- a/reports/Suhil Kiwan/solar_analysis_2026-07-11_to_2026-07-11.xlsx
+++ b/reports/Suhil Kiwan/solar_analysis_2026-07-11_to_2026-07-11.xlsx
@@ -711,16 +711,16 @@
         <v>852.62</v>
       </c>
       <c r="E9" t="n">
-        <v>833.0520691967899</v>
+        <v>833.0520691967907</v>
       </c>
       <c r="F9" t="n">
-        <v>806.0880361543324</v>
+        <v>806.0880361543323</v>
       </c>
       <c r="G9" t="n">
         <v>51.16</v>
       </c>
       <c r="H9" t="n">
-        <v>10.4716414025658</v>
+        <v>10.47164140256579</v>
       </c>
     </row>
     <row r="10">
@@ -1052,16 +1052,16 @@
         <v>852.62</v>
       </c>
       <c r="D9" t="n">
-        <v>833.0520691967899</v>
+        <v>833.0520691967907</v>
       </c>
       <c r="E9" t="n">
-        <v>806.0880361543324</v>
+        <v>806.0880361543323</v>
       </c>
       <c r="F9" t="n">
         <v>51.16</v>
       </c>
       <c r="G9" t="n">
-        <v>10.4716414025658</v>
+        <v>10.47164140256579</v>
       </c>
     </row>
     <row r="10">
@@ -24404,10 +24404,10 @@
         <v>46214.625</v>
       </c>
       <c r="B9" t="n">
-        <v>10.4716414025658</v>
+        <v>10.47164140256579</v>
       </c>
       <c r="C9" t="n">
-        <v>10.4716414025658</v>
+        <v>10.47164140256579</v>
       </c>
       <c r="D9" t="n">
         <v>8.828790000000001</v>
